--- a/Kachi_Gun/Table/Challenge.xlsx
+++ b/Kachi_Gun/Table/Challenge.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Reward_Ad_x3_Gems</t>
+          <t>Reward_Ad_x2_Gems</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -625,13 +625,13 @@
         <v>0</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
@@ -680,13 +680,13 @@
         <v>0</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" ht="19" customHeight="1">
@@ -735,13 +735,13 @@
         <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>90</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1">
@@ -790,13 +790,13 @@
         <v>0</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>120</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" ht="19" customHeight="1">
@@ -845,13 +845,13 @@
         <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>150</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1">
@@ -900,13 +900,13 @@
         <v>0</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>180</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -955,13 +955,13 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>210</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1">
@@ -1010,13 +1010,13 @@
         <v>0</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>240</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -1065,13 +1065,13 @@
         <v>0</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>270</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1">
@@ -1120,13 +1120,13 @@
         <v>0</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>300</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1">
@@ -1172,16 +1172,16 @@
         </is>
       </c>
       <c r="L12" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>335</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
@@ -1230,13 +1230,13 @@
         <v>0</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>370</v>
+        <v>210</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
@@ -1285,13 +1285,13 @@
         <v>0</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>405</v>
+        <v>230</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
@@ -1340,13 +1340,13 @@
         <v>0</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>440</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1">
@@ -1395,13 +1395,13 @@
         <v>0</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>475</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
@@ -1450,13 +1450,13 @@
         <v>0</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>510</v>
+        <v>290</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
@@ -1505,13 +1505,13 @@
         <v>0</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>545</v>
+        <v>310</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
@@ -1560,13 +1560,13 @@
         <v>0</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>580</v>
+        <v>330</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
@@ -1615,13 +1615,13 @@
         <v>0</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>615</v>
+        <v>350</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
@@ -1670,13 +1670,13 @@
         <v>0</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>650</v>
+        <v>370</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
@@ -1722,16 +1722,16 @@
         </is>
       </c>
       <c r="L22" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>690</v>
+        <v>393</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>730</v>
+        <v>416</v>
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
@@ -1835,13 +1835,13 @@
         <v>0</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>770</v>
+        <v>439</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
@@ -1890,13 +1890,13 @@
         <v>0</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>810</v>
+        <v>462</v>
       </c>
     </row>
     <row r="26" ht="19" customHeight="1">
@@ -1945,13 +1945,13 @@
         <v>0</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>850</v>
+        <v>485</v>
       </c>
     </row>
     <row r="27" ht="19" customHeight="1">
@@ -2000,13 +2000,13 @@
         <v>0</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>890</v>
+        <v>508</v>
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
@@ -2055,13 +2055,13 @@
         <v>0</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>930</v>
+        <v>531</v>
       </c>
     </row>
     <row r="29" ht="19" customHeight="1">
@@ -2110,13 +2110,13 @@
         <v>0</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>970</v>
+        <v>554</v>
       </c>
     </row>
     <row r="30" ht="19" customHeight="1">
@@ -2165,13 +2165,13 @@
         <v>0</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>1010</v>
+        <v>577</v>
       </c>
     </row>
     <row r="31" ht="19" customHeight="1">
@@ -2220,13 +2220,13 @@
         <v>0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>1050</v>
+        <v>600</v>
       </c>
     </row>
     <row r="32" ht="19" customHeight="1">
@@ -2272,16 +2272,16 @@
         </is>
       </c>
       <c r="L32" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>135</v>
+        <v>52</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>1095</v>
+        <v>626</v>
       </c>
     </row>
     <row r="33" ht="19" customHeight="1">
@@ -2330,13 +2330,13 @@
         <v>0</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>135</v>
+        <v>52</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>1140</v>
+        <v>652</v>
       </c>
     </row>
     <row r="34" ht="19" customHeight="1">
@@ -2385,13 +2385,13 @@
         <v>0</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>135</v>
+        <v>52</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>1185</v>
+        <v>678</v>
       </c>
     </row>
     <row r="35" ht="19" customHeight="1">
@@ -2440,13 +2440,13 @@
         <v>0</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>135</v>
+        <v>52</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>1230</v>
+        <v>704</v>
       </c>
     </row>
     <row r="36" ht="19" customHeight="1">
@@ -2495,13 +2495,13 @@
         <v>0</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>135</v>
+        <v>52</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>1275</v>
+        <v>730</v>
       </c>
     </row>
     <row r="37" ht="19" customHeight="1">
@@ -2550,13 +2550,13 @@
         <v>0</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>135</v>
+        <v>52</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1320</v>
+        <v>756</v>
       </c>
     </row>
     <row r="38" ht="19" customHeight="1">
@@ -2605,13 +2605,13 @@
         <v>0</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>135</v>
+        <v>52</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>1365</v>
+        <v>782</v>
       </c>
     </row>
     <row r="39" ht="19" customHeight="1">
@@ -2660,13 +2660,13 @@
         <v>0</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>135</v>
+        <v>52</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>1410</v>
+        <v>808</v>
       </c>
     </row>
     <row r="40" ht="19" customHeight="1">
@@ -2715,13 +2715,13 @@
         <v>0</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>135</v>
+        <v>52</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1455</v>
+        <v>834</v>
       </c>
     </row>
     <row r="41" ht="19" customHeight="1">
@@ -2770,13 +2770,13 @@
         <v>0</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>135</v>
+        <v>52</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1500</v>
+        <v>860</v>
       </c>
     </row>
     <row r="42" ht="19" customHeight="1">
@@ -2822,16 +2822,16 @@
         </is>
       </c>
       <c r="L42" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>150</v>
+        <v>58</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>1550</v>
+        <v>889</v>
       </c>
     </row>
     <row r="43" ht="19" customHeight="1">
@@ -2880,13 +2880,13 @@
         <v>0</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>150</v>
+        <v>58</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>1600</v>
+        <v>918</v>
       </c>
     </row>
     <row r="44" ht="19" customHeight="1">
@@ -2935,13 +2935,13 @@
         <v>0</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>150</v>
+        <v>58</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>1650</v>
+        <v>947</v>
       </c>
     </row>
     <row r="45" ht="19" customHeight="1">
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>150</v>
+        <v>58</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>1700</v>
+        <v>976</v>
       </c>
     </row>
     <row r="46" ht="19" customHeight="1">
@@ -3045,13 +3045,13 @@
         <v>0</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>150</v>
+        <v>58</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>1750</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="47" ht="19" customHeight="1">
@@ -3100,13 +3100,13 @@
         <v>0</v>
       </c>
       <c r="M47" s="3" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="N47" s="3" t="n">
-        <v>150</v>
+        <v>58</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>1800</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="48" ht="19" customHeight="1">
@@ -3155,13 +3155,13 @@
         <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>150</v>
+        <v>58</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>1850</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="49" ht="19" customHeight="1">
@@ -3210,13 +3210,13 @@
         <v>0</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>150</v>
+        <v>58</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>1900</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="50" ht="19" customHeight="1">
@@ -3265,13 +3265,13 @@
         <v>0</v>
       </c>
       <c r="M50" s="3" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="N50" s="3" t="n">
-        <v>150</v>
+        <v>58</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>1950</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="51" ht="19" customHeight="1">
@@ -3320,13 +3320,13 @@
         <v>0</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>150</v>
+        <v>58</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>2000</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="52" ht="19" customHeight="1">
@@ -3372,16 +3372,16 @@
         </is>
       </c>
       <c r="L52" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M52" s="3" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="N52" s="3" t="n">
-        <v>165</v>
+        <v>64</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>2055</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="53" ht="19" customHeight="1">
@@ -3430,13 +3430,13 @@
         <v>0</v>
       </c>
       <c r="M53" s="3" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="N53" s="3" t="n">
-        <v>165</v>
+        <v>64</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>2110</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="54" ht="19" customHeight="1">
@@ -3485,13 +3485,13 @@
         <v>0</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>165</v>
+        <v>64</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>2165</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="55" ht="19" customHeight="1">
@@ -3540,13 +3540,13 @@
         <v>0</v>
       </c>
       <c r="M55" s="3" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="N55" s="3" t="n">
-        <v>165</v>
+        <v>64</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>2220</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="56" ht="19" customHeight="1">
@@ -3595,13 +3595,13 @@
         <v>0</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>165</v>
+        <v>64</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>2275</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="57" ht="19" customHeight="1">
@@ -3650,13 +3650,13 @@
         <v>0</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>165</v>
+        <v>64</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>2330</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="58" ht="19" customHeight="1">
@@ -3705,13 +3705,13 @@
         <v>0</v>
       </c>
       <c r="M58" s="3" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>165</v>
+        <v>64</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>2385</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="59" ht="19" customHeight="1">
@@ -3760,13 +3760,13 @@
         <v>0</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>165</v>
+        <v>64</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>2440</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="60" ht="19" customHeight="1">
@@ -3815,13 +3815,13 @@
         <v>0</v>
       </c>
       <c r="M60" s="3" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="N60" s="3" t="n">
-        <v>165</v>
+        <v>64</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>2495</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="61" ht="19" customHeight="1">
@@ -3870,13 +3870,13 @@
         <v>0</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>165</v>
+        <v>64</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>2550</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="62" ht="19" customHeight="1">
@@ -3922,16 +3922,16 @@
         </is>
       </c>
       <c r="L62" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M62" s="3" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="N62" s="3" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>2610</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="63" ht="19" customHeight="1">
@@ -3980,13 +3980,13 @@
         <v>0</v>
       </c>
       <c r="M63" s="3" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="O63" s="6" t="n">
-        <v>2670</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="64" ht="19" customHeight="1">
@@ -4035,13 +4035,13 @@
         <v>0</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="O64" s="6" t="n">
-        <v>2730</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="65" ht="19" customHeight="1">
@@ -4090,13 +4090,13 @@
         <v>0</v>
       </c>
       <c r="M65" s="3" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="N65" s="3" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="O65" s="6" t="n">
-        <v>2790</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="66" ht="19" customHeight="1">
@@ -4145,13 +4145,13 @@
         <v>0</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="O66" s="6" t="n">
-        <v>2850</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="67" ht="19" customHeight="1">
@@ -4200,13 +4200,13 @@
         <v>0</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="O67" s="6" t="n">
-        <v>2910</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="68" ht="19" customHeight="1">
@@ -4255,13 +4255,13 @@
         <v>0</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="O68" s="6" t="n">
-        <v>2970</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="69" ht="19" customHeight="1">
@@ -4310,13 +4310,13 @@
         <v>0</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="O69" s="6" t="n">
-        <v>3030</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="70" ht="19" customHeight="1">
@@ -4365,13 +4365,13 @@
         <v>0</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="O70" s="6" t="n">
-        <v>3090</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="71" ht="19" customHeight="1">
@@ -4420,13 +4420,13 @@
         <v>0</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="O71" s="6" t="n">
-        <v>3150</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="72" ht="19" customHeight="1">
@@ -4472,16 +4472,16 @@
         </is>
       </c>
       <c r="L72" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>195</v>
+        <v>76</v>
       </c>
       <c r="O72" s="6" t="n">
-        <v>3215</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="73" ht="19" customHeight="1">
@@ -4530,13 +4530,13 @@
         <v>0</v>
       </c>
       <c r="M73" s="3" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="N73" s="3" t="n">
-        <v>195</v>
+        <v>76</v>
       </c>
       <c r="O73" s="6" t="n">
-        <v>3280</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="74" ht="19" customHeight="1">
@@ -4585,13 +4585,13 @@
         <v>0</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>195</v>
+        <v>76</v>
       </c>
       <c r="O74" s="6" t="n">
-        <v>3345</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="75" ht="19" customHeight="1">
@@ -4640,13 +4640,13 @@
         <v>0</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>195</v>
+        <v>76</v>
       </c>
       <c r="O75" s="6" t="n">
-        <v>3410</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="76" ht="19" customHeight="1">
@@ -4695,13 +4695,13 @@
         <v>0</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>195</v>
+        <v>76</v>
       </c>
       <c r="O76" s="6" t="n">
-        <v>3475</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="77" ht="19" customHeight="1">
@@ -4750,13 +4750,13 @@
         <v>0</v>
       </c>
       <c r="M77" s="3" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="N77" s="3" t="n">
-        <v>195</v>
+        <v>76</v>
       </c>
       <c r="O77" s="6" t="n">
-        <v>3540</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="78" ht="19" customHeight="1">
@@ -4805,13 +4805,13 @@
         <v>0</v>
       </c>
       <c r="M78" s="3" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>195</v>
+        <v>76</v>
       </c>
       <c r="O78" s="6" t="n">
-        <v>3605</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="79" ht="19" customHeight="1">
@@ -4860,13 +4860,13 @@
         <v>0</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>195</v>
+        <v>76</v>
       </c>
       <c r="O79" s="6" t="n">
-        <v>3670</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="80" ht="19" customHeight="1">
@@ -4915,13 +4915,13 @@
         <v>0</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>195</v>
+        <v>76</v>
       </c>
       <c r="O80" s="6" t="n">
-        <v>3735</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="81" ht="19" customHeight="1">
@@ -4970,13 +4970,13 @@
         <v>0</v>
       </c>
       <c r="M81" s="3" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>195</v>
+        <v>76</v>
       </c>
       <c r="O81" s="6" t="n">
-        <v>3800</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="82" ht="19" customHeight="1">
@@ -5022,16 +5022,16 @@
         </is>
       </c>
       <c r="L82" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M82" s="3" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="N82" s="3" t="n">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="O82" s="6" t="n">
-        <v>3870</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="83" ht="19" customHeight="1">
@@ -5080,13 +5080,13 @@
         <v>0</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="N83" s="3" t="n">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="O83" s="6" t="n">
-        <v>3940</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="84" ht="19" customHeight="1">
@@ -5135,13 +5135,13 @@
         <v>0</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="O84" s="6" t="n">
-        <v>4010</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="85" ht="19" customHeight="1">
@@ -5190,13 +5190,13 @@
         <v>0</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="O85" s="6" t="n">
-        <v>4080</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="86" ht="19" customHeight="1">
@@ -5245,13 +5245,13 @@
         <v>0</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="O86" s="6" t="n">
-        <v>4150</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="87" ht="19" customHeight="1">
@@ -5300,13 +5300,13 @@
         <v>0</v>
       </c>
       <c r="M87" s="3" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="N87" s="3" t="n">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="O87" s="6" t="n">
-        <v>4220</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="88" ht="19" customHeight="1">
@@ -5355,13 +5355,13 @@
         <v>0</v>
       </c>
       <c r="M88" s="3" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="O88" s="6" t="n">
-        <v>4290</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="89" ht="19" customHeight="1">
@@ -5410,13 +5410,13 @@
         <v>0</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="O89" s="6" t="n">
-        <v>4360</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="90" ht="19" customHeight="1">
@@ -5465,13 +5465,13 @@
         <v>0</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="O90" s="6" t="n">
-        <v>4430</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="91" ht="19" customHeight="1">
@@ -5520,13 +5520,13 @@
         <v>0</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="O91" s="6" t="n">
-        <v>4500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="92" ht="19" customHeight="1">
@@ -5572,16 +5572,16 @@
         </is>
       </c>
       <c r="L92" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>225</v>
+        <v>86</v>
       </c>
       <c r="O92" s="6" t="n">
-        <v>4575</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="93" ht="19" customHeight="1">
@@ -5630,13 +5630,13 @@
         <v>0</v>
       </c>
       <c r="M93" s="3" t="n">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="N93" s="3" t="n">
-        <v>225</v>
+        <v>86</v>
       </c>
       <c r="O93" s="6" t="n">
-        <v>4650</v>
+        <v>2686</v>
       </c>
     </row>
     <row r="94" ht="19" customHeight="1">
@@ -5685,13 +5685,13 @@
         <v>0</v>
       </c>
       <c r="M94" s="3" t="n">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="N94" s="3" t="n">
-        <v>225</v>
+        <v>86</v>
       </c>
       <c r="O94" s="6" t="n">
-        <v>4725</v>
+        <v>2729</v>
       </c>
     </row>
     <row r="95" ht="19" customHeight="1">
@@ -5740,13 +5740,13 @@
         <v>0</v>
       </c>
       <c r="M95" s="3" t="n">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="N95" s="3" t="n">
-        <v>225</v>
+        <v>86</v>
       </c>
       <c r="O95" s="6" t="n">
-        <v>4800</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="96" ht="19" customHeight="1">
@@ -5795,13 +5795,13 @@
         <v>0</v>
       </c>
       <c r="M96" s="3" t="n">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="N96" s="3" t="n">
-        <v>225</v>
+        <v>86</v>
       </c>
       <c r="O96" s="6" t="n">
-        <v>4875</v>
+        <v>2815</v>
       </c>
     </row>
     <row r="97" ht="19" customHeight="1">
@@ -5850,13 +5850,13 @@
         <v>0</v>
       </c>
       <c r="M97" s="3" t="n">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="N97" s="3" t="n">
-        <v>225</v>
+        <v>86</v>
       </c>
       <c r="O97" s="6" t="n">
-        <v>4950</v>
+        <v>2858</v>
       </c>
     </row>
     <row r="98" ht="19" customHeight="1">
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="M98" s="3" t="n">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="N98" s="3" t="n">
-        <v>225</v>
+        <v>86</v>
       </c>
       <c r="O98" s="6" t="n">
-        <v>5025</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="99" ht="19" customHeight="1">
@@ -5960,13 +5960,13 @@
         <v>0</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>225</v>
+        <v>86</v>
       </c>
       <c r="O99" s="6" t="n">
-        <v>5100</v>
+        <v>2944</v>
       </c>
     </row>
     <row r="100" ht="19" customHeight="1">
@@ -6015,13 +6015,13 @@
         <v>0</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>225</v>
+        <v>86</v>
       </c>
       <c r="O100" s="6" t="n">
-        <v>5175</v>
+        <v>2987</v>
       </c>
     </row>
     <row r="101" ht="19" customHeight="1">
@@ -6070,13 +6070,13 @@
         <v>0</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>225</v>
+        <v>86</v>
       </c>
       <c r="O101" s="6" t="n">
-        <v>5250</v>
+        <v>3030</v>
       </c>
     </row>
     <row r="102" ht="19" customHeight="1">
@@ -6122,16 +6122,16 @@
         </is>
       </c>
       <c r="L102" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M102" s="3" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="N102" s="3" t="n">
-        <v>240</v>
+        <v>92</v>
       </c>
       <c r="O102" s="6" t="n">
-        <v>5330</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="103" ht="19" customHeight="1">
@@ -6180,13 +6180,13 @@
         <v>0</v>
       </c>
       <c r="M103" s="3" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="N103" s="3" t="n">
-        <v>240</v>
+        <v>92</v>
       </c>
       <c r="O103" s="6" t="n">
-        <v>5410</v>
+        <v>3122</v>
       </c>
     </row>
     <row r="104" ht="19" customHeight="1">
@@ -6235,13 +6235,13 @@
         <v>0</v>
       </c>
       <c r="M104" s="3" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="N104" s="3" t="n">
-        <v>240</v>
+        <v>92</v>
       </c>
       <c r="O104" s="6" t="n">
-        <v>5490</v>
+        <v>3168</v>
       </c>
     </row>
     <row r="105" ht="19" customHeight="1">
@@ -6290,13 +6290,13 @@
         <v>0</v>
       </c>
       <c r="M105" s="3" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="N105" s="3" t="n">
-        <v>240</v>
+        <v>92</v>
       </c>
       <c r="O105" s="6" t="n">
-        <v>5570</v>
+        <v>3214</v>
       </c>
     </row>
     <row r="106" ht="19" customHeight="1">
@@ -6345,13 +6345,13 @@
         <v>0</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>240</v>
+        <v>92</v>
       </c>
       <c r="O106" s="6" t="n">
-        <v>5650</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="107" ht="19" customHeight="1">
@@ -6400,13 +6400,13 @@
         <v>0</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>240</v>
+        <v>92</v>
       </c>
       <c r="O107" s="6" t="n">
-        <v>5730</v>
+        <v>3306</v>
       </c>
     </row>
     <row r="108" ht="19" customHeight="1">
@@ -6455,13 +6455,13 @@
         <v>0</v>
       </c>
       <c r="M108" s="3" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="N108" s="3" t="n">
-        <v>240</v>
+        <v>92</v>
       </c>
       <c r="O108" s="6" t="n">
-        <v>5810</v>
+        <v>3352</v>
       </c>
     </row>
     <row r="109" ht="19" customHeight="1">
@@ -6510,13 +6510,13 @@
         <v>0</v>
       </c>
       <c r="M109" s="3" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="N109" s="3" t="n">
-        <v>240</v>
+        <v>92</v>
       </c>
       <c r="O109" s="6" t="n">
-        <v>5890</v>
+        <v>3398</v>
       </c>
     </row>
     <row r="110" ht="19" customHeight="1">
@@ -6565,13 +6565,13 @@
         <v>0</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>240</v>
+        <v>92</v>
       </c>
       <c r="O110" s="6" t="n">
-        <v>5970</v>
+        <v>3444</v>
       </c>
     </row>
     <row r="111" ht="19" customHeight="1">
@@ -6620,13 +6620,13 @@
         <v>0</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>240</v>
+        <v>92</v>
       </c>
       <c r="O111" s="6" t="n">
-        <v>6050</v>
+        <v>3490</v>
       </c>
     </row>
     <row r="112" ht="19" customHeight="1">
@@ -6672,16 +6672,16 @@
         </is>
       </c>
       <c r="L112" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>255</v>
+        <v>98</v>
       </c>
       <c r="O112" s="6" t="n">
-        <v>6135</v>
+        <v>3539</v>
       </c>
     </row>
     <row r="113" ht="19" customHeight="1">
@@ -6730,13 +6730,13 @@
         <v>0</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>255</v>
+        <v>98</v>
       </c>
       <c r="O113" s="6" t="n">
-        <v>6220</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="114" ht="19" customHeight="1">
@@ -6785,13 +6785,13 @@
         <v>0</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>255</v>
+        <v>98</v>
       </c>
       <c r="O114" s="6" t="n">
-        <v>6305</v>
+        <v>3637</v>
       </c>
     </row>
     <row r="115" ht="19" customHeight="1">
@@ -6840,13 +6840,13 @@
         <v>0</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>255</v>
+        <v>98</v>
       </c>
       <c r="O115" s="6" t="n">
-        <v>6390</v>
+        <v>3686</v>
       </c>
     </row>
     <row r="116" ht="19" customHeight="1">
@@ -6895,13 +6895,13 @@
         <v>0</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>255</v>
+        <v>98</v>
       </c>
       <c r="O116" s="6" t="n">
-        <v>6475</v>
+        <v>3735</v>
       </c>
     </row>
     <row r="117" ht="19" customHeight="1">
@@ -6950,13 +6950,13 @@
         <v>0</v>
       </c>
       <c r="M117" s="3" t="n">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="N117" s="3" t="n">
-        <v>255</v>
+        <v>98</v>
       </c>
       <c r="O117" s="6" t="n">
-        <v>6560</v>
+        <v>3784</v>
       </c>
     </row>
     <row r="118" ht="19" customHeight="1">
@@ -7005,13 +7005,13 @@
         <v>0</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>255</v>
+        <v>98</v>
       </c>
       <c r="O118" s="6" t="n">
-        <v>6645</v>
+        <v>3833</v>
       </c>
     </row>
     <row r="119" ht="19" customHeight="1">
@@ -7060,13 +7060,13 @@
         <v>0</v>
       </c>
       <c r="M119" s="3" t="n">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="N119" s="3" t="n">
-        <v>255</v>
+        <v>98</v>
       </c>
       <c r="O119" s="6" t="n">
-        <v>6730</v>
+        <v>3882</v>
       </c>
     </row>
     <row r="120" ht="19" customHeight="1">
@@ -7115,13 +7115,13 @@
         <v>0</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>255</v>
+        <v>98</v>
       </c>
       <c r="O120" s="6" t="n">
-        <v>6815</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="121" ht="19" customHeight="1">
@@ -7170,13 +7170,13 @@
         <v>0</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>255</v>
+        <v>98</v>
       </c>
       <c r="O121" s="6" t="n">
-        <v>6900</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="122" ht="19" customHeight="1">
@@ -7222,16 +7222,16 @@
         </is>
       </c>
       <c r="L122" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M122" s="3" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="N122" s="3" t="n">
-        <v>270</v>
+        <v>104</v>
       </c>
       <c r="O122" s="6" t="n">
-        <v>6990</v>
+        <v>4032</v>
       </c>
     </row>
     <row r="123" ht="19" customHeight="1">
@@ -7280,13 +7280,13 @@
         <v>0</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>270</v>
+        <v>104</v>
       </c>
       <c r="O123" s="6" t="n">
-        <v>7080</v>
+        <v>4084</v>
       </c>
     </row>
     <row r="124" ht="19" customHeight="1">
@@ -7335,13 +7335,13 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>270</v>
+        <v>104</v>
       </c>
       <c r="O124" s="6" t="n">
-        <v>7170</v>
+        <v>4136</v>
       </c>
     </row>
     <row r="125" ht="19" customHeight="1">
@@ -7390,13 +7390,13 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>270</v>
+        <v>104</v>
       </c>
       <c r="O125" s="6" t="n">
-        <v>7260</v>
+        <v>4188</v>
       </c>
     </row>
     <row r="126" ht="19" customHeight="1">
@@ -7445,13 +7445,13 @@
         <v>0</v>
       </c>
       <c r="M126" s="3" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="N126" s="3" t="n">
-        <v>270</v>
+        <v>104</v>
       </c>
       <c r="O126" s="6" t="n">
-        <v>7350</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="127" ht="19" customHeight="1">
@@ -7500,13 +7500,13 @@
         <v>0</v>
       </c>
       <c r="M127" s="3" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="N127" s="3" t="n">
-        <v>270</v>
+        <v>104</v>
       </c>
       <c r="O127" s="6" t="n">
-        <v>7440</v>
+        <v>4292</v>
       </c>
     </row>
     <row r="128" ht="19" customHeight="1">
@@ -7555,13 +7555,13 @@
         <v>0</v>
       </c>
       <c r="M128" s="3" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="N128" s="3" t="n">
-        <v>270</v>
+        <v>104</v>
       </c>
       <c r="O128" s="6" t="n">
-        <v>7530</v>
+        <v>4344</v>
       </c>
     </row>
     <row r="129" ht="19" customHeight="1">
@@ -7610,13 +7610,13 @@
         <v>0</v>
       </c>
       <c r="M129" s="3" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="N129" s="3" t="n">
-        <v>270</v>
+        <v>104</v>
       </c>
       <c r="O129" s="6" t="n">
-        <v>7620</v>
+        <v>4396</v>
       </c>
     </row>
     <row r="130" ht="19" customHeight="1">
@@ -7665,13 +7665,13 @@
         <v>0</v>
       </c>
       <c r="M130" s="3" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="N130" s="3" t="n">
-        <v>270</v>
+        <v>104</v>
       </c>
       <c r="O130" s="6" t="n">
-        <v>7710</v>
+        <v>4448</v>
       </c>
     </row>
     <row r="131" ht="19" customHeight="1">
@@ -7720,13 +7720,13 @@
         <v>0</v>
       </c>
       <c r="M131" s="3" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="N131" s="3" t="n">
-        <v>270</v>
+        <v>104</v>
       </c>
       <c r="O131" s="6" t="n">
-        <v>7800</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="132" ht="19" customHeight="1">
@@ -7772,16 +7772,16 @@
         </is>
       </c>
       <c r="L132" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M132" s="3" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="N132" s="3" t="n">
-        <v>285</v>
+        <v>110</v>
       </c>
       <c r="O132" s="6" t="n">
-        <v>7895</v>
+        <v>4555</v>
       </c>
     </row>
     <row r="133" ht="19" customHeight="1">
@@ -7830,13 +7830,13 @@
         <v>0</v>
       </c>
       <c r="M133" s="3" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="N133" s="3" t="n">
-        <v>285</v>
+        <v>110</v>
       </c>
       <c r="O133" s="6" t="n">
-        <v>7990</v>
+        <v>4610</v>
       </c>
     </row>
     <row r="134" ht="19" customHeight="1">
@@ -7885,13 +7885,13 @@
         <v>0</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>285</v>
+        <v>110</v>
       </c>
       <c r="O134" s="6" t="n">
-        <v>8085</v>
+        <v>4665</v>
       </c>
     </row>
     <row r="135" ht="19" customHeight="1">
@@ -7940,13 +7940,13 @@
         <v>0</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>285</v>
+        <v>110</v>
       </c>
       <c r="O135" s="6" t="n">
-        <v>8180</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="136" ht="19" customHeight="1">
@@ -7995,13 +7995,13 @@
         <v>0</v>
       </c>
       <c r="M136" s="3" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="N136" s="3" t="n">
-        <v>285</v>
+        <v>110</v>
       </c>
       <c r="O136" s="6" t="n">
-        <v>8275</v>
+        <v>4775</v>
       </c>
     </row>
     <row r="137" ht="19" customHeight="1">
@@ -8050,13 +8050,13 @@
         <v>0</v>
       </c>
       <c r="M137" s="3" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="N137" s="3" t="n">
-        <v>285</v>
+        <v>110</v>
       </c>
       <c r="O137" s="6" t="n">
-        <v>8370</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="138" ht="19" customHeight="1">
@@ -8105,13 +8105,13 @@
         <v>0</v>
       </c>
       <c r="M138" s="3" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="N138" s="3" t="n">
-        <v>285</v>
+        <v>110</v>
       </c>
       <c r="O138" s="6" t="n">
-        <v>8465</v>
+        <v>4885</v>
       </c>
     </row>
     <row r="139" ht="19" customHeight="1">
@@ -8160,13 +8160,13 @@
         <v>0</v>
       </c>
       <c r="M139" s="3" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="N139" s="3" t="n">
-        <v>285</v>
+        <v>110</v>
       </c>
       <c r="O139" s="6" t="n">
-        <v>8560</v>
+        <v>4940</v>
       </c>
     </row>
     <row r="140" ht="19" customHeight="1">
@@ -8215,13 +8215,13 @@
         <v>0</v>
       </c>
       <c r="M140" s="3" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="N140" s="3" t="n">
-        <v>285</v>
+        <v>110</v>
       </c>
       <c r="O140" s="6" t="n">
-        <v>8655</v>
+        <v>4995</v>
       </c>
     </row>
     <row r="141" ht="19" customHeight="1">
@@ -8270,13 +8270,13 @@
         <v>0</v>
       </c>
       <c r="M141" s="3" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="N141" s="3" t="n">
-        <v>285</v>
+        <v>110</v>
       </c>
       <c r="O141" s="6" t="n">
-        <v>8750</v>
+        <v>5050</v>
       </c>
     </row>
     <row r="142" ht="19" customHeight="1">
@@ -8322,16 +8322,16 @@
         </is>
       </c>
       <c r="L142" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M142" s="3" t="n">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="N142" s="3" t="n">
-        <v>300</v>
+        <v>116</v>
       </c>
       <c r="O142" s="6" t="n">
-        <v>8850</v>
+        <v>5108</v>
       </c>
     </row>
     <row r="143" ht="19" customHeight="1">
@@ -8380,13 +8380,13 @@
         <v>0</v>
       </c>
       <c r="M143" s="3" t="n">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="N143" s="3" t="n">
-        <v>300</v>
+        <v>116</v>
       </c>
       <c r="O143" s="6" t="n">
-        <v>8950</v>
+        <v>5166</v>
       </c>
     </row>
     <row r="144" ht="19" customHeight="1">
@@ -8435,13 +8435,13 @@
         <v>0</v>
       </c>
       <c r="M144" s="3" t="n">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="N144" s="3" t="n">
-        <v>300</v>
+        <v>116</v>
       </c>
       <c r="O144" s="6" t="n">
-        <v>9050</v>
+        <v>5224</v>
       </c>
     </row>
     <row r="145" ht="19" customHeight="1">
@@ -8490,13 +8490,13 @@
         <v>0</v>
       </c>
       <c r="M145" s="3" t="n">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="N145" s="3" t="n">
-        <v>300</v>
+        <v>116</v>
       </c>
       <c r="O145" s="6" t="n">
-        <v>9150</v>
+        <v>5282</v>
       </c>
     </row>
     <row r="146" ht="19" customHeight="1">
@@ -8545,13 +8545,13 @@
         <v>0</v>
       </c>
       <c r="M146" s="3" t="n">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="N146" s="3" t="n">
-        <v>300</v>
+        <v>116</v>
       </c>
       <c r="O146" s="6" t="n">
-        <v>9250</v>
+        <v>5340</v>
       </c>
     </row>
     <row r="147" ht="19" customHeight="1">
@@ -8600,13 +8600,13 @@
         <v>0</v>
       </c>
       <c r="M147" s="3" t="n">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="N147" s="3" t="n">
-        <v>300</v>
+        <v>116</v>
       </c>
       <c r="O147" s="6" t="n">
-        <v>9350</v>
+        <v>5398</v>
       </c>
     </row>
     <row r="148" ht="19" customHeight="1">
@@ -8655,13 +8655,13 @@
         <v>0</v>
       </c>
       <c r="M148" s="3" t="n">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="N148" s="3" t="n">
-        <v>300</v>
+        <v>116</v>
       </c>
       <c r="O148" s="6" t="n">
-        <v>9450</v>
+        <v>5456</v>
       </c>
     </row>
     <row r="149" ht="19" customHeight="1">
@@ -8710,13 +8710,13 @@
         <v>0</v>
       </c>
       <c r="M149" s="3" t="n">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="N149" s="3" t="n">
-        <v>300</v>
+        <v>116</v>
       </c>
       <c r="O149" s="6" t="n">
-        <v>9550</v>
+        <v>5514</v>
       </c>
     </row>
     <row r="150" ht="19" customHeight="1">
@@ -8765,13 +8765,13 @@
         <v>0</v>
       </c>
       <c r="M150" s="3" t="n">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="N150" s="3" t="n">
-        <v>300</v>
+        <v>116</v>
       </c>
       <c r="O150" s="6" t="n">
-        <v>9650</v>
+        <v>5572</v>
       </c>
     </row>
     <row r="151" ht="19" customHeight="1">
@@ -8820,13 +8820,13 @@
         <v>0</v>
       </c>
       <c r="M151" s="3" t="n">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="N151" s="3" t="n">
-        <v>300</v>
+        <v>116</v>
       </c>
       <c r="O151" s="6" t="n">
-        <v>9750</v>
+        <v>5630</v>
       </c>
     </row>
   </sheetData>

--- a/Kachi_Gun/Table/Challenge.xlsx
+++ b/Kachi_Gun/Table/Challenge.xlsx
@@ -625,13 +625,13 @@
         <v>0</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
@@ -680,13 +680,13 @@
         <v>0</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" ht="19" customHeight="1">
@@ -735,13 +735,13 @@
         <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>51</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1">
@@ -790,13 +790,13 @@
         <v>0</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>68</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" ht="19" customHeight="1">
@@ -845,13 +845,13 @@
         <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>85</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1">
@@ -900,13 +900,13 @@
         <v>0</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>102</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -955,13 +955,13 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>119</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1">
@@ -1010,13 +1010,13 @@
         <v>0</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>136</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -1065,13 +1065,13 @@
         <v>0</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>153</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1">
@@ -1120,13 +1120,13 @@
         <v>0</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>170</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1">
@@ -1172,16 +1172,16 @@
         </is>
       </c>
       <c r="L12" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>190</v>
+        <v>291</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
@@ -1230,13 +1230,13 @@
         <v>0</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>210</v>
+        <v>322</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
@@ -1285,13 +1285,13 @@
         <v>0</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>230</v>
+        <v>353</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
@@ -1340,13 +1340,13 @@
         <v>0</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>250</v>
+        <v>384</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1">
@@ -1395,13 +1395,13 @@
         <v>0</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>270</v>
+        <v>415</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
@@ -1450,13 +1450,13 @@
         <v>0</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>290</v>
+        <v>446</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
@@ -1505,13 +1505,13 @@
         <v>0</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>310</v>
+        <v>477</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
@@ -1560,13 +1560,13 @@
         <v>0</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>330</v>
+        <v>508</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
@@ -1615,13 +1615,13 @@
         <v>0</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>350</v>
+        <v>539</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
@@ -1670,13 +1670,13 @@
         <v>0</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>370</v>
+        <v>570</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
@@ -1722,16 +1722,16 @@
         </is>
       </c>
       <c r="L22" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>393</v>
+        <v>605</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>416</v>
+        <v>640</v>
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
@@ -1835,13 +1835,13 @@
         <v>0</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>439</v>
+        <v>675</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
@@ -1890,13 +1890,13 @@
         <v>0</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>462</v>
+        <v>710</v>
       </c>
     </row>
     <row r="26" ht="19" customHeight="1">
@@ -1945,13 +1945,13 @@
         <v>0</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>485</v>
+        <v>745</v>
       </c>
     </row>
     <row r="27" ht="19" customHeight="1">
@@ -2000,13 +2000,13 @@
         <v>0</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>508</v>
+        <v>780</v>
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
@@ -2055,13 +2055,13 @@
         <v>0</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>531</v>
+        <v>815</v>
       </c>
     </row>
     <row r="29" ht="19" customHeight="1">
@@ -2110,13 +2110,13 @@
         <v>0</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>554</v>
+        <v>850</v>
       </c>
     </row>
     <row r="30" ht="19" customHeight="1">
@@ -2165,13 +2165,13 @@
         <v>0</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>577</v>
+        <v>885</v>
       </c>
     </row>
     <row r="31" ht="19" customHeight="1">
@@ -2220,13 +2220,13 @@
         <v>0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="32" ht="19" customHeight="1">
@@ -2272,16 +2272,16 @@
         </is>
       </c>
       <c r="L32" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>626</v>
+        <v>960</v>
       </c>
     </row>
     <row r="33" ht="19" customHeight="1">
@@ -2330,13 +2330,13 @@
         <v>0</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>652</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="34" ht="19" customHeight="1">
@@ -2385,13 +2385,13 @@
         <v>0</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>678</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="35" ht="19" customHeight="1">
@@ -2440,13 +2440,13 @@
         <v>0</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>704</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="36" ht="19" customHeight="1">
@@ -2495,13 +2495,13 @@
         <v>0</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>730</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="37" ht="19" customHeight="1">
@@ -2550,13 +2550,13 @@
         <v>0</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>756</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="38" ht="19" customHeight="1">
@@ -2605,13 +2605,13 @@
         <v>0</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>782</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="39" ht="19" customHeight="1">
@@ -2660,13 +2660,13 @@
         <v>0</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>808</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="40" ht="19" customHeight="1">
@@ -2715,13 +2715,13 @@
         <v>0</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>834</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="41" ht="19" customHeight="1">
@@ -2770,13 +2770,13 @@
         <v>0</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>860</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="42" ht="19" customHeight="1">
@@ -2822,16 +2822,16 @@
         </is>
       </c>
       <c r="L42" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>889</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="43" ht="19" customHeight="1">
@@ -2880,13 +2880,13 @@
         <v>0</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>918</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="44" ht="19" customHeight="1">
@@ -2935,13 +2935,13 @@
         <v>0</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>947</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="45" ht="19" customHeight="1">
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>976</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="46" ht="19" customHeight="1">
@@ -3045,13 +3045,13 @@
         <v>0</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>1005</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="47" ht="19" customHeight="1">
@@ -3100,13 +3100,13 @@
         <v>0</v>
       </c>
       <c r="M47" s="3" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="N47" s="3" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>1034</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="48" ht="19" customHeight="1">
@@ -3155,13 +3155,13 @@
         <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>1063</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="49" ht="19" customHeight="1">
@@ -3210,13 +3210,13 @@
         <v>0</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>1092</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="50" ht="19" customHeight="1">
@@ -3265,13 +3265,13 @@
         <v>0</v>
       </c>
       <c r="M50" s="3" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="N50" s="3" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>1121</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="51" ht="19" customHeight="1">
@@ -3320,13 +3320,13 @@
         <v>0</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>1150</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="52" ht="19" customHeight="1">
@@ -3372,16 +3372,16 @@
         </is>
       </c>
       <c r="L52" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M52" s="3" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="N52" s="3" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>1182</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="53" ht="19" customHeight="1">
@@ -3430,13 +3430,13 @@
         <v>0</v>
       </c>
       <c r="M53" s="3" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="N53" s="3" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>1214</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="54" ht="19" customHeight="1">
@@ -3485,13 +3485,13 @@
         <v>0</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>1246</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="55" ht="19" customHeight="1">
@@ -3540,13 +3540,13 @@
         <v>0</v>
       </c>
       <c r="M55" s="3" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="N55" s="3" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>1278</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="56" ht="19" customHeight="1">
@@ -3595,13 +3595,13 @@
         <v>0</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>1310</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="57" ht="19" customHeight="1">
@@ -3650,13 +3650,13 @@
         <v>0</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>1342</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="58" ht="19" customHeight="1">
@@ -3705,13 +3705,13 @@
         <v>0</v>
       </c>
       <c r="M58" s="3" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>1374</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="59" ht="19" customHeight="1">
@@ -3760,13 +3760,13 @@
         <v>0</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>1406</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="60" ht="19" customHeight="1">
@@ -3815,13 +3815,13 @@
         <v>0</v>
       </c>
       <c r="M60" s="3" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="N60" s="3" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>1438</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="61" ht="19" customHeight="1">
@@ -3870,13 +3870,13 @@
         <v>0</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>1470</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="62" ht="19" customHeight="1">
@@ -3922,16 +3922,16 @@
         </is>
       </c>
       <c r="L62" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M62" s="3" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="N62" s="3" t="n">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>1505</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="63" ht="19" customHeight="1">
@@ -3980,13 +3980,13 @@
         <v>0</v>
       </c>
       <c r="M63" s="3" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="O63" s="6" t="n">
-        <v>1540</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="64" ht="19" customHeight="1">
@@ -4035,13 +4035,13 @@
         <v>0</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="O64" s="6" t="n">
-        <v>1575</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="65" ht="19" customHeight="1">
@@ -4090,13 +4090,13 @@
         <v>0</v>
       </c>
       <c r="M65" s="3" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="N65" s="3" t="n">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="O65" s="6" t="n">
-        <v>1610</v>
+        <v>2452</v>
       </c>
     </row>
     <row r="66" ht="19" customHeight="1">
@@ -4145,13 +4145,13 @@
         <v>0</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="O66" s="6" t="n">
-        <v>1645</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="67" ht="19" customHeight="1">
@@ -4200,13 +4200,13 @@
         <v>0</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="O67" s="6" t="n">
-        <v>1680</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="68" ht="19" customHeight="1">
@@ -4255,13 +4255,13 @@
         <v>0</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="O68" s="6" t="n">
-        <v>1715</v>
+        <v>2611</v>
       </c>
     </row>
     <row r="69" ht="19" customHeight="1">
@@ -4310,13 +4310,13 @@
         <v>0</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="O69" s="6" t="n">
-        <v>1750</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="70" ht="19" customHeight="1">
@@ -4365,13 +4365,13 @@
         <v>0</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="O70" s="6" t="n">
-        <v>1785</v>
+        <v>2717</v>
       </c>
     </row>
     <row r="71" ht="19" customHeight="1">
@@ -4420,13 +4420,13 @@
         <v>0</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="O71" s="6" t="n">
-        <v>1820</v>
+        <v>2770</v>
       </c>
     </row>
     <row r="72" ht="19" customHeight="1">
@@ -4472,16 +4472,16 @@
         </is>
       </c>
       <c r="L72" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="O72" s="6" t="n">
-        <v>1858</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="73" ht="19" customHeight="1">
@@ -4530,13 +4530,13 @@
         <v>0</v>
       </c>
       <c r="M73" s="3" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="N73" s="3" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="O73" s="6" t="n">
-        <v>1896</v>
+        <v>2884</v>
       </c>
     </row>
     <row r="74" ht="19" customHeight="1">
@@ -4585,13 +4585,13 @@
         <v>0</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="O74" s="6" t="n">
-        <v>1934</v>
+        <v>2941</v>
       </c>
     </row>
     <row r="75" ht="19" customHeight="1">
@@ -4640,13 +4640,13 @@
         <v>0</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="O75" s="6" t="n">
-        <v>1972</v>
+        <v>2998</v>
       </c>
     </row>
     <row r="76" ht="19" customHeight="1">
@@ -4695,13 +4695,13 @@
         <v>0</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="O76" s="6" t="n">
-        <v>2010</v>
+        <v>3055</v>
       </c>
     </row>
     <row r="77" ht="19" customHeight="1">
@@ -4750,13 +4750,13 @@
         <v>0</v>
       </c>
       <c r="M77" s="3" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="N77" s="3" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="O77" s="6" t="n">
-        <v>2048</v>
+        <v>3112</v>
       </c>
     </row>
     <row r="78" ht="19" customHeight="1">
@@ -4805,13 +4805,13 @@
         <v>0</v>
       </c>
       <c r="M78" s="3" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="O78" s="6" t="n">
-        <v>2086</v>
+        <v>3169</v>
       </c>
     </row>
     <row r="79" ht="19" customHeight="1">
@@ -4860,13 +4860,13 @@
         <v>0</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="O79" s="6" t="n">
-        <v>2124</v>
+        <v>3226</v>
       </c>
     </row>
     <row r="80" ht="19" customHeight="1">
@@ -4915,13 +4915,13 @@
         <v>0</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="O80" s="6" t="n">
-        <v>2162</v>
+        <v>3283</v>
       </c>
     </row>
     <row r="81" ht="19" customHeight="1">
@@ -4970,13 +4970,13 @@
         <v>0</v>
       </c>
       <c r="M81" s="3" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="O81" s="6" t="n">
-        <v>2200</v>
+        <v>3340</v>
       </c>
     </row>
     <row r="82" ht="19" customHeight="1">
@@ -5022,16 +5022,16 @@
         </is>
       </c>
       <c r="L82" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M82" s="3" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="N82" s="3" t="n">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="O82" s="6" t="n">
-        <v>2240</v>
+        <v>3402</v>
       </c>
     </row>
     <row r="83" ht="19" customHeight="1">
@@ -5080,13 +5080,13 @@
         <v>0</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="N83" s="3" t="n">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="O83" s="6" t="n">
-        <v>2280</v>
+        <v>3464</v>
       </c>
     </row>
     <row r="84" ht="19" customHeight="1">
@@ -5135,13 +5135,13 @@
         <v>0</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="O84" s="6" t="n">
-        <v>2320</v>
+        <v>3526</v>
       </c>
     </row>
     <row r="85" ht="19" customHeight="1">
@@ -5190,13 +5190,13 @@
         <v>0</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="O85" s="6" t="n">
-        <v>2360</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="86" ht="19" customHeight="1">
@@ -5245,13 +5245,13 @@
         <v>0</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="O86" s="6" t="n">
-        <v>2400</v>
+        <v>3650</v>
       </c>
     </row>
     <row r="87" ht="19" customHeight="1">
@@ -5300,13 +5300,13 @@
         <v>0</v>
       </c>
       <c r="M87" s="3" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="N87" s="3" t="n">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="O87" s="6" t="n">
-        <v>2440</v>
+        <v>3712</v>
       </c>
     </row>
     <row r="88" ht="19" customHeight="1">
@@ -5355,13 +5355,13 @@
         <v>0</v>
       </c>
       <c r="M88" s="3" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="O88" s="6" t="n">
-        <v>2480</v>
+        <v>3774</v>
       </c>
     </row>
     <row r="89" ht="19" customHeight="1">
@@ -5410,13 +5410,13 @@
         <v>0</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="O89" s="6" t="n">
-        <v>2520</v>
+        <v>3836</v>
       </c>
     </row>
     <row r="90" ht="19" customHeight="1">
@@ -5465,13 +5465,13 @@
         <v>0</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="O90" s="6" t="n">
-        <v>2560</v>
+        <v>3898</v>
       </c>
     </row>
     <row r="91" ht="19" customHeight="1">
@@ -5520,13 +5520,13 @@
         <v>0</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="O91" s="6" t="n">
-        <v>2600</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="92" ht="19" customHeight="1">
@@ -5572,16 +5572,16 @@
         </is>
       </c>
       <c r="L92" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="O92" s="6" t="n">
-        <v>2643</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="93" ht="19" customHeight="1">
@@ -5630,13 +5630,13 @@
         <v>0</v>
       </c>
       <c r="M93" s="3" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="N93" s="3" t="n">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="O93" s="6" t="n">
-        <v>2686</v>
+        <v>4092</v>
       </c>
     </row>
     <row r="94" ht="19" customHeight="1">
@@ -5685,13 +5685,13 @@
         <v>0</v>
       </c>
       <c r="M94" s="3" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="N94" s="3" t="n">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="O94" s="6" t="n">
-        <v>2729</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="95" ht="19" customHeight="1">
@@ -5740,13 +5740,13 @@
         <v>0</v>
       </c>
       <c r="M95" s="3" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="N95" s="3" t="n">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="O95" s="6" t="n">
-        <v>2772</v>
+        <v>4224</v>
       </c>
     </row>
     <row r="96" ht="19" customHeight="1">
@@ -5795,13 +5795,13 @@
         <v>0</v>
       </c>
       <c r="M96" s="3" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="N96" s="3" t="n">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="O96" s="6" t="n">
-        <v>2815</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="97" ht="19" customHeight="1">
@@ -5850,13 +5850,13 @@
         <v>0</v>
       </c>
       <c r="M97" s="3" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="N97" s="3" t="n">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="O97" s="6" t="n">
-        <v>2858</v>
+        <v>4356</v>
       </c>
     </row>
     <row r="98" ht="19" customHeight="1">
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="M98" s="3" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="N98" s="3" t="n">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="O98" s="6" t="n">
-        <v>2901</v>
+        <v>4422</v>
       </c>
     </row>
     <row r="99" ht="19" customHeight="1">
@@ -5960,13 +5960,13 @@
         <v>0</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="O99" s="6" t="n">
-        <v>2944</v>
+        <v>4488</v>
       </c>
     </row>
     <row r="100" ht="19" customHeight="1">
@@ -6015,13 +6015,13 @@
         <v>0</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="O100" s="6" t="n">
-        <v>2987</v>
+        <v>4554</v>
       </c>
     </row>
     <row r="101" ht="19" customHeight="1">
@@ -6070,13 +6070,13 @@
         <v>0</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="O101" s="6" t="n">
-        <v>3030</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="102" ht="19" customHeight="1">
@@ -6122,16 +6122,16 @@
         </is>
       </c>
       <c r="L102" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M102" s="3" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="N102" s="3" t="n">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="O102" s="6" t="n">
-        <v>3076</v>
+        <v>4690</v>
       </c>
     </row>
     <row r="103" ht="19" customHeight="1">
@@ -6180,13 +6180,13 @@
         <v>0</v>
       </c>
       <c r="M103" s="3" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="N103" s="3" t="n">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="O103" s="6" t="n">
-        <v>3122</v>
+        <v>4760</v>
       </c>
     </row>
     <row r="104" ht="19" customHeight="1">
@@ -6235,13 +6235,13 @@
         <v>0</v>
       </c>
       <c r="M104" s="3" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="N104" s="3" t="n">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="O104" s="6" t="n">
-        <v>3168</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="105" ht="19" customHeight="1">
@@ -6290,13 +6290,13 @@
         <v>0</v>
       </c>
       <c r="M105" s="3" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="N105" s="3" t="n">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="O105" s="6" t="n">
-        <v>3214</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="106" ht="19" customHeight="1">
@@ -6345,13 +6345,13 @@
         <v>0</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="O106" s="6" t="n">
-        <v>3260</v>
+        <v>4970</v>
       </c>
     </row>
     <row r="107" ht="19" customHeight="1">
@@ -6400,13 +6400,13 @@
         <v>0</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="O107" s="6" t="n">
-        <v>3306</v>
+        <v>5040</v>
       </c>
     </row>
     <row r="108" ht="19" customHeight="1">
@@ -6455,13 +6455,13 @@
         <v>0</v>
       </c>
       <c r="M108" s="3" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="N108" s="3" t="n">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="O108" s="6" t="n">
-        <v>3352</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="109" ht="19" customHeight="1">
@@ -6510,13 +6510,13 @@
         <v>0</v>
       </c>
       <c r="M109" s="3" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="N109" s="3" t="n">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="O109" s="6" t="n">
-        <v>3398</v>
+        <v>5180</v>
       </c>
     </row>
     <row r="110" ht="19" customHeight="1">
@@ -6565,13 +6565,13 @@
         <v>0</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="O110" s="6" t="n">
-        <v>3444</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="111" ht="19" customHeight="1">
@@ -6620,13 +6620,13 @@
         <v>0</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="O111" s="6" t="n">
-        <v>3490</v>
+        <v>5320</v>
       </c>
     </row>
     <row r="112" ht="19" customHeight="1">
@@ -6672,16 +6672,16 @@
         </is>
       </c>
       <c r="L112" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="O112" s="6" t="n">
-        <v>3539</v>
+        <v>5395</v>
       </c>
     </row>
     <row r="113" ht="19" customHeight="1">
@@ -6730,13 +6730,13 @@
         <v>0</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="O113" s="6" t="n">
-        <v>3588</v>
+        <v>5470</v>
       </c>
     </row>
     <row r="114" ht="19" customHeight="1">
@@ -6785,13 +6785,13 @@
         <v>0</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="O114" s="6" t="n">
-        <v>3637</v>
+        <v>5545</v>
       </c>
     </row>
     <row r="115" ht="19" customHeight="1">
@@ -6840,13 +6840,13 @@
         <v>0</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="O115" s="6" t="n">
-        <v>3686</v>
+        <v>5620</v>
       </c>
     </row>
     <row r="116" ht="19" customHeight="1">
@@ -6895,13 +6895,13 @@
         <v>0</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="O116" s="6" t="n">
-        <v>3735</v>
+        <v>5695</v>
       </c>
     </row>
     <row r="117" ht="19" customHeight="1">
@@ -6950,13 +6950,13 @@
         <v>0</v>
       </c>
       <c r="M117" s="3" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="N117" s="3" t="n">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="O117" s="6" t="n">
-        <v>3784</v>
+        <v>5770</v>
       </c>
     </row>
     <row r="118" ht="19" customHeight="1">
@@ -7005,13 +7005,13 @@
         <v>0</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="O118" s="6" t="n">
-        <v>3833</v>
+        <v>5845</v>
       </c>
     </row>
     <row r="119" ht="19" customHeight="1">
@@ -7060,13 +7060,13 @@
         <v>0</v>
       </c>
       <c r="M119" s="3" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="N119" s="3" t="n">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="O119" s="6" t="n">
-        <v>3882</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="120" ht="19" customHeight="1">
@@ -7115,13 +7115,13 @@
         <v>0</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="O120" s="6" t="n">
-        <v>3931</v>
+        <v>5995</v>
       </c>
     </row>
     <row r="121" ht="19" customHeight="1">
@@ -7170,13 +7170,13 @@
         <v>0</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="O121" s="6" t="n">
-        <v>3980</v>
+        <v>6070</v>
       </c>
     </row>
     <row r="122" ht="19" customHeight="1">
@@ -7222,16 +7222,16 @@
         </is>
       </c>
       <c r="L122" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M122" s="3" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="N122" s="3" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="O122" s="6" t="n">
-        <v>4032</v>
+        <v>6149</v>
       </c>
     </row>
     <row r="123" ht="19" customHeight="1">
@@ -7280,13 +7280,13 @@
         <v>0</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="O123" s="6" t="n">
-        <v>4084</v>
+        <v>6228</v>
       </c>
     </row>
     <row r="124" ht="19" customHeight="1">
@@ -7335,13 +7335,13 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="O124" s="6" t="n">
-        <v>4136</v>
+        <v>6307</v>
       </c>
     </row>
     <row r="125" ht="19" customHeight="1">
@@ -7390,13 +7390,13 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="O125" s="6" t="n">
-        <v>4188</v>
+        <v>6386</v>
       </c>
     </row>
     <row r="126" ht="19" customHeight="1">
@@ -7445,13 +7445,13 @@
         <v>0</v>
       </c>
       <c r="M126" s="3" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="N126" s="3" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="O126" s="6" t="n">
-        <v>4240</v>
+        <v>6465</v>
       </c>
     </row>
     <row r="127" ht="19" customHeight="1">
@@ -7500,13 +7500,13 @@
         <v>0</v>
       </c>
       <c r="M127" s="3" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="N127" s="3" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="O127" s="6" t="n">
-        <v>4292</v>
+        <v>6544</v>
       </c>
     </row>
     <row r="128" ht="19" customHeight="1">
@@ -7555,13 +7555,13 @@
         <v>0</v>
       </c>
       <c r="M128" s="3" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="N128" s="3" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="O128" s="6" t="n">
-        <v>4344</v>
+        <v>6623</v>
       </c>
     </row>
     <row r="129" ht="19" customHeight="1">
@@ -7610,13 +7610,13 @@
         <v>0</v>
       </c>
       <c r="M129" s="3" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="N129" s="3" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="O129" s="6" t="n">
-        <v>4396</v>
+        <v>6702</v>
       </c>
     </row>
     <row r="130" ht="19" customHeight="1">
@@ -7665,13 +7665,13 @@
         <v>0</v>
       </c>
       <c r="M130" s="3" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="N130" s="3" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="O130" s="6" t="n">
-        <v>4448</v>
+        <v>6781</v>
       </c>
     </row>
     <row r="131" ht="19" customHeight="1">
@@ -7720,13 +7720,13 @@
         <v>0</v>
       </c>
       <c r="M131" s="3" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="N131" s="3" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="O131" s="6" t="n">
-        <v>4500</v>
+        <v>6860</v>
       </c>
     </row>
     <row r="132" ht="19" customHeight="1">
@@ -7772,16 +7772,16 @@
         </is>
       </c>
       <c r="L132" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M132" s="3" t="n">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="N132" s="3" t="n">
-        <v>110</v>
+        <v>168</v>
       </c>
       <c r="O132" s="6" t="n">
-        <v>4555</v>
+        <v>6944</v>
       </c>
     </row>
     <row r="133" ht="19" customHeight="1">
@@ -7830,13 +7830,13 @@
         <v>0</v>
       </c>
       <c r="M133" s="3" t="n">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="N133" s="3" t="n">
-        <v>110</v>
+        <v>168</v>
       </c>
       <c r="O133" s="6" t="n">
-        <v>4610</v>
+        <v>7028</v>
       </c>
     </row>
     <row r="134" ht="19" customHeight="1">
@@ -7885,13 +7885,13 @@
         <v>0</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>110</v>
+        <v>168</v>
       </c>
       <c r="O134" s="6" t="n">
-        <v>4665</v>
+        <v>7112</v>
       </c>
     </row>
     <row r="135" ht="19" customHeight="1">
@@ -7940,13 +7940,13 @@
         <v>0</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>110</v>
+        <v>168</v>
       </c>
       <c r="O135" s="6" t="n">
-        <v>4720</v>
+        <v>7196</v>
       </c>
     </row>
     <row r="136" ht="19" customHeight="1">
@@ -7995,13 +7995,13 @@
         <v>0</v>
       </c>
       <c r="M136" s="3" t="n">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="N136" s="3" t="n">
-        <v>110</v>
+        <v>168</v>
       </c>
       <c r="O136" s="6" t="n">
-        <v>4775</v>
+        <v>7280</v>
       </c>
     </row>
     <row r="137" ht="19" customHeight="1">
@@ -8050,13 +8050,13 @@
         <v>0</v>
       </c>
       <c r="M137" s="3" t="n">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="N137" s="3" t="n">
-        <v>110</v>
+        <v>168</v>
       </c>
       <c r="O137" s="6" t="n">
-        <v>4830</v>
+        <v>7364</v>
       </c>
     </row>
     <row r="138" ht="19" customHeight="1">
@@ -8105,13 +8105,13 @@
         <v>0</v>
       </c>
       <c r="M138" s="3" t="n">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="N138" s="3" t="n">
-        <v>110</v>
+        <v>168</v>
       </c>
       <c r="O138" s="6" t="n">
-        <v>4885</v>
+        <v>7448</v>
       </c>
     </row>
     <row r="139" ht="19" customHeight="1">
@@ -8160,13 +8160,13 @@
         <v>0</v>
       </c>
       <c r="M139" s="3" t="n">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="N139" s="3" t="n">
-        <v>110</v>
+        <v>168</v>
       </c>
       <c r="O139" s="6" t="n">
-        <v>4940</v>
+        <v>7532</v>
       </c>
     </row>
     <row r="140" ht="19" customHeight="1">
@@ -8215,13 +8215,13 @@
         <v>0</v>
       </c>
       <c r="M140" s="3" t="n">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="N140" s="3" t="n">
-        <v>110</v>
+        <v>168</v>
       </c>
       <c r="O140" s="6" t="n">
-        <v>4995</v>
+        <v>7616</v>
       </c>
     </row>
     <row r="141" ht="19" customHeight="1">
@@ -8270,13 +8270,13 @@
         <v>0</v>
       </c>
       <c r="M141" s="3" t="n">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="N141" s="3" t="n">
-        <v>110</v>
+        <v>168</v>
       </c>
       <c r="O141" s="6" t="n">
-        <v>5050</v>
+        <v>7700</v>
       </c>
     </row>
     <row r="142" ht="19" customHeight="1">
@@ -8322,16 +8322,16 @@
         </is>
       </c>
       <c r="L142" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M142" s="3" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="N142" s="3" t="n">
-        <v>116</v>
+        <v>176</v>
       </c>
       <c r="O142" s="6" t="n">
-        <v>5108</v>
+        <v>7788</v>
       </c>
     </row>
     <row r="143" ht="19" customHeight="1">
@@ -8380,13 +8380,13 @@
         <v>0</v>
       </c>
       <c r="M143" s="3" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="N143" s="3" t="n">
-        <v>116</v>
+        <v>176</v>
       </c>
       <c r="O143" s="6" t="n">
-        <v>5166</v>
+        <v>7876</v>
       </c>
     </row>
     <row r="144" ht="19" customHeight="1">
@@ -8435,13 +8435,13 @@
         <v>0</v>
       </c>
       <c r="M144" s="3" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="N144" s="3" t="n">
-        <v>116</v>
+        <v>176</v>
       </c>
       <c r="O144" s="6" t="n">
-        <v>5224</v>
+        <v>7964</v>
       </c>
     </row>
     <row r="145" ht="19" customHeight="1">
@@ -8490,13 +8490,13 @@
         <v>0</v>
       </c>
       <c r="M145" s="3" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="N145" s="3" t="n">
-        <v>116</v>
+        <v>176</v>
       </c>
       <c r="O145" s="6" t="n">
-        <v>5282</v>
+        <v>8052</v>
       </c>
     </row>
     <row r="146" ht="19" customHeight="1">
@@ -8545,13 +8545,13 @@
         <v>0</v>
       </c>
       <c r="M146" s="3" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="N146" s="3" t="n">
-        <v>116</v>
+        <v>176</v>
       </c>
       <c r="O146" s="6" t="n">
-        <v>5340</v>
+        <v>8140</v>
       </c>
     </row>
     <row r="147" ht="19" customHeight="1">
@@ -8600,13 +8600,13 @@
         <v>0</v>
       </c>
       <c r="M147" s="3" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="N147" s="3" t="n">
-        <v>116</v>
+        <v>176</v>
       </c>
       <c r="O147" s="6" t="n">
-        <v>5398</v>
+        <v>8228</v>
       </c>
     </row>
     <row r="148" ht="19" customHeight="1">
@@ -8655,13 +8655,13 @@
         <v>0</v>
       </c>
       <c r="M148" s="3" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="N148" s="3" t="n">
-        <v>116</v>
+        <v>176</v>
       </c>
       <c r="O148" s="6" t="n">
-        <v>5456</v>
+        <v>8316</v>
       </c>
     </row>
     <row r="149" ht="19" customHeight="1">
@@ -8710,13 +8710,13 @@
         <v>0</v>
       </c>
       <c r="M149" s="3" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="N149" s="3" t="n">
-        <v>116</v>
+        <v>176</v>
       </c>
       <c r="O149" s="6" t="n">
-        <v>5514</v>
+        <v>8404</v>
       </c>
     </row>
     <row r="150" ht="19" customHeight="1">
@@ -8765,13 +8765,13 @@
         <v>0</v>
       </c>
       <c r="M150" s="3" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="N150" s="3" t="n">
-        <v>116</v>
+        <v>176</v>
       </c>
       <c r="O150" s="6" t="n">
-        <v>5572</v>
+        <v>8492</v>
       </c>
     </row>
     <row r="151" ht="19" customHeight="1">
@@ -8820,13 +8820,13 @@
         <v>0</v>
       </c>
       <c r="M151" s="3" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="N151" s="3" t="n">
-        <v>116</v>
+        <v>176</v>
       </c>
       <c r="O151" s="6" t="n">
-        <v>5630</v>
+        <v>8580</v>
       </c>
     </row>
   </sheetData>
